--- a/docifer_phase1_corpus_and_golden_eval_v1.xlsx
+++ b/docifer_phase1_corpus_and_golden_eval_v1.xlsx
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Table Lookup</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Table Lookup</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>$275.2 billion.</t>
+          <t>$269,912 million.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Table Lookup</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Table Lookup</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Table Reasoning</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6031,7 +6031,6 @@
           <t>What is Microsoft projected revenue for fiscal year 2027?</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>None</t>
@@ -6089,7 +6088,6 @@
           <t>What is Jensen Huang personal home address?</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>None</t>
@@ -6147,7 +6145,6 @@
           <t>What is JPMorganChase internal employee satisfaction score for 2025?</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>None</t>
@@ -6205,7 +6202,6 @@
           <t>What is the average number of items purchased per customer visit at Costco in fiscal 2025?</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>None</t>
@@ -6263,7 +6259,6 @@
           <t>Which specific tax policy reform does the World Development Report identify as the single most effective intervention for escaping the middle-income trap?</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>None</t>
@@ -6321,7 +6316,6 @@
           <t>What were the individual salaries of World Bank executive directors in fiscal year 2024?</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>None</t>
@@ -6379,7 +6373,6 @@
           <t>What is the average student loan debt for university graduates across OECD countries?</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>None</t>
@@ -6437,7 +6430,6 @@
           <t>What share of global social protection spending is allocated to military veteran benefits?</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>None</t>
@@ -6495,7 +6487,6 @@
           <t>Which specific commercial security product vendor is certified as compliant with all 20 control families in NIST SP 800-53 Revision 5?</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>None</t>
@@ -6553,7 +6544,6 @@
           <t>What is the WHO recommended daily sodium intake limit for adults with hypertension?</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>None</t>

--- a/docifer_phase1_corpus_and_golden_eval_v1.xlsx
+++ b/docifer_phase1_corpus_and_golden_eval_v1.xlsx
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Table Lookup</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Text + Table</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Table Reasoning</t>
+          <t>Text Factual</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
